--- a/Impact Soundworks/Bravura Scoring Brass/xlsx/01 Ensemble.xlsx
+++ b/Impact Soundworks/Bravura Scoring Brass/xlsx/01 Ensemble.xlsx
@@ -38,6 +38,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -60,6 +75,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -88,6 +118,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -110,6 +155,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,6 +198,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -160,6 +235,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,6 +278,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -204,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="168">
   <si>
     <t>Name</t>
   </si>
@@ -691,13 +796,37 @@
   <si>
     <t>Flutter</t>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>01 Ensemble Full Brass</t>
+  </si>
+  <si>
+    <t>02 Ensemble Trumpets</t>
+  </si>
+  <si>
+    <t>03 Ensemble Horns</t>
+  </si>
+  <si>
+    <t>04 Ensemble Trombones</t>
+  </si>
+  <si>
+    <t>05 Ensemble Low Brass</t>
+  </si>
+  <si>
+    <t>06 Ensemble Orchestrator</t>
+  </si>
+  <si>
+    <t>07 Ensemble Chordmaker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -742,8 +871,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -796,6 +932,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEEF4"/>
         <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -855,7 +997,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,6 +1057,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1005,13 +1153,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1310,7 +1458,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1319,7 +1467,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -1332,100 +1480,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -1433,12 +1540,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -1446,13 +1549,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -1461,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -1473,13 +1576,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -1488,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -1499,26 +1602,54 @@
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="12">
+        <v>120</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -3097,26 +3228,55 @@
       <c r="J129" s="12"/>
       <c r="K129" s="12"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="12"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="5"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -3135,7 +3295,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -3144,7 +3304,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -3153,7 +3313,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3164,7 +3324,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -3177,100 +3337,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -3278,12 +3397,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -3291,13 +3406,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -3306,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -3318,13 +3433,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -3333,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -3345,13 +3460,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -3360,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -3372,13 +3487,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -3387,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -3399,13 +3514,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -3414,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -3426,13 +3541,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>12</v>
@@ -3441,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G10" s="12">
         <v>120</v>
@@ -3453,13 +3568,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>12</v>
@@ -3468,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" s="12">
         <v>120</v>
@@ -3480,13 +3595,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>12</v>
@@ -3495,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G12" s="12">
         <v>120</v>
@@ -3506,26 +3621,54 @@
       <c r="K12" s="12"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="12">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="12">
+        <v>120</v>
+      </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="12">
+        <v>120</v>
+      </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
@@ -5039,26 +5182,55 @@
       <c r="J130" s="12"/>
       <c r="K130" s="12"/>
     </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="12"/>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="1"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B130">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B132">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5076,7 +5248,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F130</xm:sqref>
+          <xm:sqref>F4:F132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -5085,7 +5257,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E130</xm:sqref>
+          <xm:sqref>E4:E132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -5094,7 +5266,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D130</xm:sqref>
+          <xm:sqref>D4:D132</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5105,7 +5277,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -5118,100 +5290,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -5219,12 +5350,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -5232,13 +5359,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -5247,7 +5374,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -5259,13 +5386,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -5274,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -5286,13 +5413,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -5301,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -5313,13 +5440,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -5328,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -5340,13 +5467,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -5355,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -5367,13 +5494,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>12</v>
@@ -5382,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G10" s="12">
         <v>120</v>
@@ -5394,13 +5521,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B11" s="12">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>12</v>
@@ -5409,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" s="12">
         <v>120</v>
@@ -5421,13 +5548,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B12" s="12">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>12</v>
@@ -5436,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G12" s="12">
         <v>120</v>
@@ -5448,13 +5575,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B13" s="12">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>159</v>
+      <c r="C13" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>12</v>
@@ -5463,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" s="12">
         <v>120</v>
@@ -5474,26 +5601,54 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="12">
+        <v>120</v>
+      </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="A15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="12">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="12">
+        <v>120</v>
+      </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
@@ -6994,26 +7149,55 @@
       <c r="J130" s="12"/>
       <c r="K130" s="12"/>
     </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="12"/>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="1"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B130">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B132">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K130">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K132">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -7031,7 +7215,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D130</xm:sqref>
+          <xm:sqref>D4:D132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -7040,7 +7224,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E130</xm:sqref>
+          <xm:sqref>E4:E132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -7049,7 +7233,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F130</xm:sqref>
+          <xm:sqref>F4:F132</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7060,7 +7244,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -7073,100 +7257,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -7174,12 +7317,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -7187,13 +7326,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -7202,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -7214,13 +7353,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -7229,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -7241,13 +7380,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -7256,7 +7395,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -7268,13 +7407,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>159</v>
+      <c r="C8" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -7283,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -7294,26 +7433,54 @@
       <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="12">
+        <v>120</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
@@ -8814,26 +8981,55 @@
       <c r="J125" s="12"/>
       <c r="K125" s="12"/>
     </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="1"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="1"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
+      <c r="I127" s="12"/>
+      <c r="J127" s="12"/>
+      <c r="K127" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K125">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K127">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J125">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J127">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G125">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G127">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I125">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I127">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B125">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B127">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8851,7 +9047,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F125</xm:sqref>
+          <xm:sqref>F4:F127</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8860,7 +9056,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E125</xm:sqref>
+          <xm:sqref>E4:E127</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8869,7 +9065,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D125</xm:sqref>
+          <xm:sqref>D4:D127</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8880,7 +9076,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -8893,100 +9089,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -8994,12 +9149,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -9007,13 +9158,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -9022,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -9034,13 +9185,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -9049,7 +9200,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -9061,13 +9212,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -9076,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" s="12">
         <v>120</v>
@@ -9088,13 +9239,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
@@ -9103,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G8" s="12">
         <v>120</v>
@@ -9115,13 +9266,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>12</v>
@@ -9130,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G9" s="12">
         <v>120</v>
@@ -9141,26 +9292,54 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="12">
+        <v>120</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="12">
+        <v>120</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
@@ -10596,26 +10775,55 @@
       <c r="J121" s="12"/>
       <c r="K121" s="12"/>
     </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="1"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="1"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B121">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B123">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K121">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K123">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -10633,7 +10841,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D121</xm:sqref>
+          <xm:sqref>D4:D123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -10642,7 +10850,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E121</xm:sqref>
+          <xm:sqref>E4:E123</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -10651,7 +10859,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F121</xm:sqref>
+          <xm:sqref>F4:F123</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10662,7 +10870,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -10675,100 +10883,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -10776,12 +10943,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -10789,13 +10952,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -10804,7 +10967,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -10816,13 +10979,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -10831,7 +10994,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -10842,26 +11005,54 @@
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="12">
+        <v>120</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -12284,26 +12475,55 @@
       <c r="J117" s="12"/>
       <c r="K117" s="12"/>
     </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="1"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="1"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B117">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B119">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12321,7 +12541,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F117</xm:sqref>
+          <xm:sqref>F4:F119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12330,7 +12550,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E117</xm:sqref>
+          <xm:sqref>E4:E119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12339,7 +12559,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D117</xm:sqref>
+          <xm:sqref>D4:D119</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12349,7 +12569,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="14" customWidth="1"/>
@@ -12362,100 +12582,59 @@
     <col min="1026" max="16384" width="8.875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="12">
-        <v>120</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -12463,12 +12642,8 @@
       <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="12">
-        <v>120</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -12476,13 +12651,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -12491,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12">
         <v>120</v>
@@ -12503,13 +12678,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -12518,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12">
         <v>120</v>
@@ -12529,26 +12704,54 @@
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="12">
+        <v>120</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12">
+        <v>120</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -13971,26 +14174,55 @@
       <c r="J117" s="12"/>
       <c r="K117" s="12"/>
     </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="1"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="1"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="6"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B117">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B119">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K117">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K119">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -14008,7 +14240,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D117</xm:sqref>
+          <xm:sqref>D4:D119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -14017,7 +14249,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E117</xm:sqref>
+          <xm:sqref>E4:E119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -14026,7 +14258,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F117</xm:sqref>
+          <xm:sqref>F4:F119</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
